--- a/data/ai/authoring/mapping.xlsx
+++ b/data/ai/authoring/mapping.xlsx
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Vendor ai uses data it is exposed to for helping with internal processes.</t>
+          <t>The business purpose each vendor AI feature serves in internal processes is decided and owned.</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
